--- a/AAII_Financials/Yearly/BORAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BORAY_YR_FIN.xlsx
@@ -1935,10 +1935,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>209000</v>
+        <v>208400</v>
       </c>
       <c r="E59" s="3">
-        <v>273900</v>
+        <v>270300</v>
       </c>
       <c r="F59" s="3">
         <v>206100</v>
